--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100700</v>
+        <v>100703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106640</v>
+        <v>106643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106640</v>
+        <v>106643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106640</v>
+        <v>106643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100703</v>
+        <v>100704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106643</v>
+        <v>106644</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106643</v>
+        <v>106644</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106643</v>
+        <v>106644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 705-2023 artfynd.xlsx
+++ b/artfynd/S 705-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>136116952</v>
       </c>
       <c r="B3" t="n">
-        <v>100704</v>
+        <v>100709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136117001</v>
       </c>
       <c r="B9" t="n">
-        <v>106644</v>
+        <v>106649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>136117026</v>
       </c>
       <c r="B10" t="n">
-        <v>106644</v>
+        <v>106649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>136117070</v>
       </c>
       <c r="B11" t="n">
-        <v>106644</v>
+        <v>106649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
